--- a/docs/Column name category.xlsx
+++ b/docs/Column name category.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/korosh/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/korosh/Desktop/ivs/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4557C9C3-DA82-B245-8E3C-6E3D918633F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD296EC-125D-4148-A439-877B2F590C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="875" xr2:uid="{2A85EC4D-8378-9548-AEED-756653D41DB5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" tabRatio="875" xr2:uid="{2A85EC4D-8378-9548-AEED-756653D41DB5}"/>
   </bookViews>
   <sheets>
     <sheet name="COLUMNS_202604291159" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="Projects" sheetId="3" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'COLUMNS_202604291159'!$A$1:$B$617</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">'COLUMNS_202604291159'!$A$1:$B$618</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3187" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="819">
   <si>
     <t>Column1</t>
   </si>
@@ -2460,6 +2460,54 @@
   </si>
   <si>
     <t>View will be removed</t>
+  </si>
+  <si>
+    <t>ContractStatusName</t>
+  </si>
+  <si>
+    <t>ContractedStartDate_MiladiDate</t>
+  </si>
+  <si>
+    <t>ContractFinishDate_MiladiDate</t>
+  </si>
+  <si>
+    <t>ContractAmount</t>
+  </si>
+  <si>
+    <t>ContractFinalAmount</t>
+  </si>
+  <si>
+    <t>SumContractAmendment</t>
+  </si>
+  <si>
+    <t>ContractDate_MiladiDate</t>
+  </si>
+  <si>
+    <t>AmountPayment</t>
+  </si>
+  <si>
+    <t>AmountInvoice</t>
+  </si>
+  <si>
+    <t>CountContractAmendment</t>
+  </si>
+  <si>
+    <t>CountInvoice</t>
+  </si>
+  <si>
+    <t>MaxAmendmentDate_MiladiDate</t>
+  </si>
+  <si>
+    <t>MaxInvoice_MiladiDate</t>
+  </si>
+  <si>
+    <t>CountPayment</t>
+  </si>
+  <si>
+    <t>MaxPaiementDate_MiladiDate</t>
+  </si>
+  <si>
+    <t>IsCashIn</t>
   </si>
 </sst>
 </file>
@@ -2657,7 +2705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2685,6 +2733,7 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2733,8 +2782,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9BD59974-066F-FC4F-8162-76A947D327DD}" name="COLUMNS_202604291159" displayName="COLUMNS_202604291159" ref="A1:E617" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:E617" xr:uid="{9BD59974-066F-FC4F-8162-76A947D327DD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9BD59974-066F-FC4F-8162-76A947D327DD}" name="COLUMNS_202604291159" displayName="COLUMNS_202604291159" ref="A1:E618" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:E618" xr:uid="{9BD59974-066F-FC4F-8162-76A947D327DD}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A8AC0F6A-23EA-FC40-9565-68820802D3D7}" uniqueName="1" name="Column1" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{CB77A6E1-6A62-2648-A471-C0B999F8AF48}" uniqueName="2" name="Column2" queryTableFieldId="2" dataDxfId="3"/>
@@ -3043,7 +3092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355900C4-27A9-854A-90B2-17D3FBB01249}">
-  <dimension ref="A1:E610"/>
+  <dimension ref="A1:E611"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" customWidth="1"/>
@@ -3458,7 +3507,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>44</v>
+        <v>715</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>715</v>
@@ -3469,35 +3518,35 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="43" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+    <row r="43" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>500</v>
-      </c>
+      <c r="B43" s="27" t="s">
+        <v>818</v>
+      </c>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
     </row>
     <row r="44" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>22</v>
+        <v>787</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="45" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -3505,32 +3554,32 @@
         <v>41</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>48</v>
+        <v>336</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="46" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+    <row r="47" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C46" s="4" t="s">
+      <c r="B47" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>716</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C47" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="48" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3538,7 +3587,7 @@
         <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
         <v>708</v>
@@ -3549,32 +3598,32 @@
         <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="50" spans="1:3" s="3" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C50" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="51" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" s="3" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>717</v>
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="52" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3582,10 +3631,10 @@
         <v>41</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C52" t="s">
-        <v>708</v>
+        <v>804</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="53" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3593,7 +3642,7 @@
         <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C53" t="s">
         <v>708</v>
@@ -3604,7 +3653,7 @@
         <v>41</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C54" t="s">
         <v>708</v>
@@ -3615,7 +3664,7 @@
         <v>41</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
         <v>708</v>
@@ -3626,21 +3675,21 @@
         <v>41</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C56" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>718</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="58" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3648,21 +3697,21 @@
         <v>41</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="C58" s="4" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>720</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="60" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -3670,32 +3719,32 @@
         <v>41</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>63</v>
+        <v>806</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>807</v>
+      </c>
+      <c r="C61" s="6" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="61" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="7" t="s">
+    <row r="62" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="7" t="s">
+      <c r="B62" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>729</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3703,7 +3752,7 @@
         <v>41</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C63" t="s">
         <v>708</v>
@@ -3714,7 +3763,7 @@
         <v>41</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C64" t="s">
         <v>708</v>
@@ -3725,65 +3774,65 @@
         <v>41</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="66" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
+    <row r="67" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="B67" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="67" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="8" t="s">
+    <row r="68" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="8" t="s">
+      <c r="B68" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="68" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="7" t="s">
+    <row r="69" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C68" s="7" t="s">
+      <c r="B69" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="69" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="8" t="s">
+    <row r="70" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="8" t="s">
+      <c r="B70" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>725</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="71" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -3791,7 +3840,7 @@
         <v>41</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C71" t="s">
         <v>708</v>
@@ -3802,7 +3851,7 @@
         <v>41</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C72" t="s">
         <v>708</v>
@@ -3813,21 +3862,21 @@
         <v>41</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C73" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>726</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C74" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="75" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
@@ -3835,7 +3884,7 @@
         <v>41</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C75" t="s">
         <v>708</v>
@@ -3846,7 +3895,7 @@
         <v>41</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C76" t="s">
         <v>708</v>
@@ -3857,21 +3906,21 @@
         <v>41</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C77" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>730</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="79" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -3879,10 +3928,10 @@
         <v>41</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C79" t="s">
-        <v>708</v>
+        <v>816</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="80" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -3890,7 +3939,7 @@
         <v>41</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C80" t="s">
         <v>708</v>
@@ -3901,7 +3950,7 @@
         <v>41</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C81" t="s">
         <v>708</v>
@@ -3912,21 +3961,21 @@
         <v>41</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C82" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>732</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="84" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -3934,7 +3983,7 @@
         <v>41</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>733</v>
@@ -3945,7 +3994,7 @@
         <v>41</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>733</v>
@@ -3956,7 +4005,7 @@
         <v>41</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>733</v>
@@ -3967,7 +4016,7 @@
         <v>41</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>733</v>
@@ -3978,7 +4027,7 @@
         <v>41</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>733</v>
@@ -3989,24 +4038,21 @@
         <v>41</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>93</v>
-      </c>
-      <c r="B90" t="s">
-        <v>94</v>
-      </c>
-      <c r="C90" t="s">
-        <v>734</v>
-      </c>
-      <c r="D90" t="s">
-        <v>793</v>
+    <row r="90" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -4014,7 +4060,10 @@
         <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>40</v>
+        <v>94</v>
+      </c>
+      <c r="C91" t="s">
+        <v>734</v>
       </c>
       <c r="D91" t="s">
         <v>793</v>
@@ -4025,7 +4074,7 @@
         <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="D92" t="s">
         <v>793</v>
@@ -4036,10 +4085,7 @@
         <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>96</v>
-      </c>
-      <c r="C93" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="D93" t="s">
         <v>793</v>
@@ -4050,7 +4096,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="C94" t="s">
+        <v>22</v>
       </c>
       <c r="D94" t="s">
         <v>793</v>
@@ -4061,10 +4110,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
-      </c>
-      <c r="C95" t="s">
-        <v>714</v>
+        <v>97</v>
       </c>
       <c r="D95" t="s">
         <v>793</v>
@@ -4075,10 +4121,10 @@
         <v>93</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C96" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
       <c r="D96" t="s">
         <v>793</v>
@@ -4089,7 +4135,10 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="C97" t="s">
+        <v>736</v>
       </c>
       <c r="D97" t="s">
         <v>793</v>
@@ -4100,7 +4149,7 @@
         <v>93</v>
       </c>
       <c r="B98" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D98" t="s">
         <v>793</v>
@@ -4111,10 +4160,7 @@
         <v>93</v>
       </c>
       <c r="B99" t="s">
-        <v>102</v>
-      </c>
-      <c r="C99" t="s">
-        <v>708</v>
+        <v>101</v>
       </c>
       <c r="D99" t="s">
         <v>793</v>
@@ -4125,7 +4171,7 @@
         <v>93</v>
       </c>
       <c r="B100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C100" t="s">
         <v>708</v>
@@ -4139,7 +4185,7 @@
         <v>93</v>
       </c>
       <c r="B101" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C101" t="s">
         <v>708</v>
@@ -4153,7 +4199,7 @@
         <v>93</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C102" t="s">
         <v>708</v>
@@ -4167,7 +4213,7 @@
         <v>93</v>
       </c>
       <c r="B103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C103" t="s">
         <v>708</v>
@@ -4181,10 +4227,10 @@
         <v>93</v>
       </c>
       <c r="B104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C104" t="s">
-        <v>737</v>
+        <v>708</v>
       </c>
       <c r="D104" t="s">
         <v>793</v>
@@ -4195,10 +4241,10 @@
         <v>93</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C105" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
       <c r="D105" t="s">
         <v>793</v>
@@ -4209,7 +4255,7 @@
         <v>93</v>
       </c>
       <c r="B106" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C106" t="s">
         <v>708</v>
@@ -4223,7 +4269,7 @@
         <v>93</v>
       </c>
       <c r="B107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C107" t="s">
         <v>708</v>
@@ -4237,7 +4283,7 @@
         <v>93</v>
       </c>
       <c r="B108" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C108" t="s">
         <v>708</v>
@@ -4251,7 +4297,7 @@
         <v>93</v>
       </c>
       <c r="B109" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C109" t="s">
         <v>708</v>
@@ -4265,10 +4311,10 @@
         <v>93</v>
       </c>
       <c r="B110" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C110" t="s">
-        <v>794</v>
+        <v>708</v>
       </c>
       <c r="D110" t="s">
         <v>793</v>
@@ -4279,10 +4325,10 @@
         <v>93</v>
       </c>
       <c r="B111" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C111" t="s">
-        <v>708</v>
+        <v>794</v>
       </c>
       <c r="D111" t="s">
         <v>793</v>
@@ -4293,7 +4339,7 @@
         <v>93</v>
       </c>
       <c r="B112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C112" t="s">
         <v>708</v>
@@ -4307,7 +4353,7 @@
         <v>93</v>
       </c>
       <c r="B113" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C113" t="s">
         <v>708</v>
@@ -4321,7 +4367,7 @@
         <v>93</v>
       </c>
       <c r="B114" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C114" t="s">
         <v>708</v>
@@ -4335,7 +4381,7 @@
         <v>93</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C115" t="s">
         <v>708</v>
@@ -4349,10 +4395,10 @@
         <v>93</v>
       </c>
       <c r="B116" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C116" t="s">
-        <v>300</v>
+        <v>708</v>
       </c>
       <c r="D116" t="s">
         <v>793</v>
@@ -4363,10 +4409,10 @@
         <v>93</v>
       </c>
       <c r="B117" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C117" t="s">
-        <v>708</v>
+        <v>300</v>
       </c>
       <c r="D117" t="s">
         <v>793</v>
@@ -4377,7 +4423,7 @@
         <v>93</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C118" t="s">
         <v>708</v>
@@ -4391,7 +4437,7 @@
         <v>93</v>
       </c>
       <c r="B119" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C119" t="s">
         <v>708</v>
@@ -4405,7 +4451,7 @@
         <v>93</v>
       </c>
       <c r="B120" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C120" t="s">
         <v>708</v>
@@ -4419,7 +4465,7 @@
         <v>93</v>
       </c>
       <c r="B121" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C121" t="s">
         <v>708</v>
@@ -4433,10 +4479,10 @@
         <v>93</v>
       </c>
       <c r="B122" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C122" t="s">
-        <v>305</v>
+        <v>708</v>
       </c>
       <c r="D122" t="s">
         <v>793</v>
@@ -4447,7 +4493,10 @@
         <v>93</v>
       </c>
       <c r="B123" t="s">
-        <v>126</v>
+        <v>125</v>
+      </c>
+      <c r="C123" t="s">
+        <v>305</v>
       </c>
       <c r="D123" t="s">
         <v>793</v>
@@ -4458,7 +4507,7 @@
         <v>93</v>
       </c>
       <c r="B124" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D124" t="s">
         <v>793</v>
@@ -4469,7 +4518,7 @@
         <v>93</v>
       </c>
       <c r="B125" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D125" t="s">
         <v>793</v>
@@ -4480,10 +4529,7 @@
         <v>93</v>
       </c>
       <c r="B126" t="s">
-        <v>129</v>
-      </c>
-      <c r="C126" t="s">
-        <v>792</v>
+        <v>128</v>
       </c>
       <c r="D126" t="s">
         <v>793</v>
@@ -4494,10 +4540,10 @@
         <v>93</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C127" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D127" t="s">
         <v>793</v>
@@ -4508,10 +4554,10 @@
         <v>93</v>
       </c>
       <c r="B128" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C128" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D128" t="s">
         <v>793</v>
@@ -4522,10 +4568,10 @@
         <v>93</v>
       </c>
       <c r="B129" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C129" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D129" t="s">
         <v>793</v>
@@ -4536,10 +4582,10 @@
         <v>93</v>
       </c>
       <c r="B130" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C130" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D130" t="s">
         <v>793</v>
@@ -4550,10 +4596,10 @@
         <v>93</v>
       </c>
       <c r="B131" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C131" t="s">
-        <v>708</v>
+        <v>797</v>
       </c>
       <c r="D131" t="s">
         <v>793</v>
@@ -4564,10 +4610,10 @@
         <v>93</v>
       </c>
       <c r="B132" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C132" t="s">
-        <v>799</v>
+        <v>708</v>
       </c>
       <c r="D132" t="s">
         <v>793</v>
@@ -4578,18 +4624,21 @@
         <v>93</v>
       </c>
       <c r="B133" t="s">
-        <v>800</v>
+        <v>135</v>
+      </c>
+      <c r="C133" t="s">
+        <v>799</v>
+      </c>
+      <c r="D133" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="B134" t="s">
-        <v>137</v>
-      </c>
-      <c r="D134" t="s">
-        <v>739</v>
+        <v>800</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
@@ -4597,7 +4646,7 @@
         <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D135" t="s">
         <v>739</v>
@@ -4608,7 +4657,7 @@
         <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D136" t="s">
         <v>739</v>
@@ -4619,7 +4668,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>139</v>
+        <v>22</v>
       </c>
       <c r="D137" t="s">
         <v>739</v>
@@ -4627,10 +4676,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D138" t="s">
         <v>739</v>
@@ -4641,7 +4690,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D139" t="s">
         <v>739</v>
@@ -4652,7 +4701,7 @@
         <v>140</v>
       </c>
       <c r="B140" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D140" t="s">
         <v>739</v>
@@ -4663,7 +4712,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="D141" t="s">
         <v>739</v>
@@ -4674,7 +4723,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D142" t="s">
         <v>739</v>
@@ -4685,7 +4734,7 @@
         <v>140</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D143" t="s">
         <v>739</v>
@@ -4693,10 +4742,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D144" t="s">
         <v>739</v>
@@ -4707,7 +4756,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D145" t="s">
         <v>739</v>
@@ -4718,7 +4767,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D146" t="s">
         <v>739</v>
@@ -4729,7 +4778,7 @@
         <v>144</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="D147" t="s">
         <v>739</v>
@@ -4740,7 +4789,7 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D148" t="s">
         <v>739</v>
@@ -4751,7 +4800,7 @@
         <v>144</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D149" t="s">
         <v>739</v>
@@ -4762,7 +4811,7 @@
         <v>144</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D150" t="s">
         <v>739</v>
@@ -4773,7 +4822,7 @@
         <v>144</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D151" t="s">
         <v>739</v>
@@ -4781,10 +4830,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B152" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D152" t="s">
         <v>739</v>
@@ -4795,7 +4844,7 @@
         <v>150</v>
       </c>
       <c r="B153" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D153" t="s">
         <v>739</v>
@@ -4806,7 +4855,7 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D154" t="s">
         <v>739</v>
@@ -4817,7 +4866,7 @@
         <v>150</v>
       </c>
       <c r="B155" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="D155" t="s">
         <v>739</v>
@@ -4828,7 +4877,7 @@
         <v>150</v>
       </c>
       <c r="B156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D156" t="s">
         <v>739</v>
@@ -4839,7 +4888,7 @@
         <v>150</v>
       </c>
       <c r="B157" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D157" t="s">
         <v>739</v>
@@ -4850,7 +4899,7 @@
         <v>150</v>
       </c>
       <c r="B158" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D158" t="s">
         <v>739</v>
@@ -4858,10 +4907,10 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B159" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D159" t="s">
         <v>739</v>
@@ -4872,7 +4921,7 @@
         <v>155</v>
       </c>
       <c r="B160" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D160" t="s">
         <v>739</v>
@@ -4883,7 +4932,7 @@
         <v>155</v>
       </c>
       <c r="B161" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D161" t="s">
         <v>739</v>
@@ -4894,7 +4943,7 @@
         <v>155</v>
       </c>
       <c r="B162" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="D162" t="s">
         <v>739</v>
@@ -4902,10 +4951,10 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B163" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D163" t="s">
         <v>739</v>
@@ -4916,7 +4965,7 @@
         <v>157</v>
       </c>
       <c r="B164" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D164" t="s">
         <v>739</v>
@@ -4927,7 +4976,7 @@
         <v>157</v>
       </c>
       <c r="B165" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D165" t="s">
         <v>739</v>
@@ -4938,7 +4987,7 @@
         <v>157</v>
       </c>
       <c r="B166" t="s">
-        <v>158</v>
+        <v>22</v>
       </c>
       <c r="D166" t="s">
         <v>739</v>
@@ -4946,10 +4995,10 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B167" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D167" t="s">
         <v>739</v>
@@ -4960,7 +5009,7 @@
         <v>159</v>
       </c>
       <c r="B168" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D168" t="s">
         <v>739</v>
@@ -4971,7 +5020,7 @@
         <v>159</v>
       </c>
       <c r="B169" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D169" t="s">
         <v>739</v>
@@ -4982,7 +5031,7 @@
         <v>159</v>
       </c>
       <c r="B170" t="s">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="D170" t="s">
         <v>739</v>
@@ -4990,10 +5039,10 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B171" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="D171" t="s">
         <v>739</v>
@@ -5004,7 +5053,7 @@
         <v>161</v>
       </c>
       <c r="B172" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D172" t="s">
         <v>739</v>
@@ -5015,7 +5064,7 @@
         <v>161</v>
       </c>
       <c r="B173" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D173" t="s">
         <v>739</v>
@@ -5026,7 +5075,7 @@
         <v>161</v>
       </c>
       <c r="B174" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="D174" t="s">
         <v>739</v>
@@ -5037,7 +5086,7 @@
         <v>161</v>
       </c>
       <c r="B175" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D175" t="s">
         <v>739</v>
@@ -5048,7 +5097,7 @@
         <v>161</v>
       </c>
       <c r="B176" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D176" t="s">
         <v>739</v>
@@ -5059,7 +5108,7 @@
         <v>161</v>
       </c>
       <c r="B177" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D177" t="s">
         <v>739</v>
@@ -5070,7 +5119,7 @@
         <v>161</v>
       </c>
       <c r="B178" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D178" t="s">
         <v>739</v>
@@ -5081,7 +5130,7 @@
         <v>161</v>
       </c>
       <c r="B179" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="D179" t="s">
         <v>739</v>
@@ -5092,7 +5141,7 @@
         <v>161</v>
       </c>
       <c r="B180" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D180" t="s">
         <v>739</v>
@@ -5103,7 +5152,7 @@
         <v>161</v>
       </c>
       <c r="B181" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D181" t="s">
         <v>739</v>
@@ -5114,7 +5163,7 @@
         <v>161</v>
       </c>
       <c r="B182" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D182" t="s">
         <v>739</v>
@@ -5122,10 +5171,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B183" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D183" t="s">
         <v>739</v>
@@ -5136,7 +5185,7 @@
         <v>166</v>
       </c>
       <c r="B184" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D184" t="s">
         <v>739</v>
@@ -5147,7 +5196,7 @@
         <v>166</v>
       </c>
       <c r="B185" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D185" t="s">
         <v>739</v>
@@ -5158,7 +5207,7 @@
         <v>166</v>
       </c>
       <c r="B186" t="s">
-        <v>167</v>
+        <v>22</v>
       </c>
       <c r="D186" t="s">
         <v>739</v>
@@ -5169,7 +5218,7 @@
         <v>166</v>
       </c>
       <c r="B187" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D187" t="s">
         <v>739</v>
@@ -5180,7 +5229,7 @@
         <v>166</v>
       </c>
       <c r="B188" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D188" t="s">
         <v>739</v>
@@ -5191,7 +5240,7 @@
         <v>166</v>
       </c>
       <c r="B189" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D189" t="s">
         <v>739</v>
@@ -5202,7 +5251,7 @@
         <v>166</v>
       </c>
       <c r="B190" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D190" t="s">
         <v>739</v>
@@ -5213,7 +5262,7 @@
         <v>166</v>
       </c>
       <c r="B191" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D191" t="s">
         <v>739</v>
@@ -5224,7 +5273,7 @@
         <v>166</v>
       </c>
       <c r="B192" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D192" t="s">
         <v>739</v>
@@ -5235,7 +5284,7 @@
         <v>166</v>
       </c>
       <c r="B193" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D193" t="s">
         <v>739</v>
@@ -5243,10 +5292,10 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B194" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="D194" t="s">
         <v>739</v>
@@ -5257,7 +5306,7 @@
         <v>175</v>
       </c>
       <c r="B195" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D195" t="s">
         <v>739</v>
@@ -5268,7 +5317,7 @@
         <v>175</v>
       </c>
       <c r="B196" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D196" t="s">
         <v>739</v>
@@ -5279,7 +5328,7 @@
         <v>175</v>
       </c>
       <c r="B197" t="s">
-        <v>176</v>
+        <v>22</v>
       </c>
       <c r="D197" t="s">
         <v>739</v>
@@ -5290,7 +5339,7 @@
         <v>175</v>
       </c>
       <c r="B198" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D198" t="s">
         <v>739</v>
@@ -5301,7 +5350,7 @@
         <v>175</v>
       </c>
       <c r="B199" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D199" t="s">
         <v>739</v>
@@ -5312,7 +5361,7 @@
         <v>175</v>
       </c>
       <c r="B200" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D200" t="s">
         <v>739</v>
@@ -5323,7 +5372,7 @@
         <v>175</v>
       </c>
       <c r="B201" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D201" t="s">
         <v>739</v>
@@ -5334,7 +5383,7 @@
         <v>175</v>
       </c>
       <c r="B202" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D202" t="s">
         <v>739</v>
@@ -5342,10 +5391,10 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B203" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="D203" t="s">
         <v>739</v>
@@ -5356,7 +5405,7 @@
         <v>182</v>
       </c>
       <c r="B204" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D204" t="s">
         <v>739</v>
@@ -5367,7 +5416,7 @@
         <v>182</v>
       </c>
       <c r="B205" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="D205" t="s">
         <v>739</v>
@@ -5378,7 +5427,7 @@
         <v>182</v>
       </c>
       <c r="B206" t="s">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="D206" t="s">
         <v>739</v>
@@ -5386,13 +5435,13 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B207" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D207" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
@@ -5400,168 +5449,171 @@
         <v>183</v>
       </c>
       <c r="B208" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D208" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>183</v>
       </c>
       <c r="B209" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+      <c r="D209" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>183</v>
       </c>
       <c r="B210" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>183</v>
       </c>
       <c r="B211" t="s">
-        <v>188</v>
-      </c>
-      <c r="C211" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>183</v>
       </c>
       <c r="B212" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+      <c r="C212" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>183</v>
       </c>
       <c r="B213" t="s">
-        <v>190</v>
-      </c>
-      <c r="C213" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>183</v>
       </c>
       <c r="B214" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C214" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>183</v>
       </c>
       <c r="B215" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C215" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>183</v>
       </c>
       <c r="B216" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C216" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>183</v>
       </c>
       <c r="B217" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C217" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>183</v>
       </c>
       <c r="B218" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+      <c r="C218" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>183</v>
       </c>
       <c r="B219" t="s">
-        <v>196</v>
-      </c>
-      <c r="C219" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>183</v>
       </c>
       <c r="B220" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C220" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>183</v>
       </c>
       <c r="B221" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C221" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>183</v>
       </c>
       <c r="B222" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C222" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>183</v>
       </c>
       <c r="B223" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+      <c r="C223" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>183</v>
       </c>
       <c r="B224" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
@@ -5569,7 +5621,7 @@
         <v>183</v>
       </c>
       <c r="B225" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.2">
@@ -5577,10 +5629,7 @@
         <v>183</v>
       </c>
       <c r="B226" t="s">
-        <v>203</v>
-      </c>
-      <c r="C226" t="s">
-        <v>705</v>
+        <v>202</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
@@ -5588,7 +5637,10 @@
         <v>183</v>
       </c>
       <c r="B227" t="s">
-        <v>26</v>
+        <v>203</v>
+      </c>
+      <c r="C227" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
@@ -5596,7 +5648,7 @@
         <v>183</v>
       </c>
       <c r="B228" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
@@ -5604,13 +5656,7 @@
         <v>183</v>
       </c>
       <c r="B229" t="s">
-        <v>205</v>
-      </c>
-      <c r="C229" t="s">
-        <v>788</v>
-      </c>
-      <c r="D229" t="s">
-        <v>708</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
@@ -5618,10 +5664,10 @@
         <v>183</v>
       </c>
       <c r="B230" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C230" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D230" t="s">
         <v>708</v>
@@ -5629,13 +5675,16 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="B231" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C231" t="s">
-        <v>741</v>
+        <v>789</v>
+      </c>
+      <c r="D231" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
@@ -5643,7 +5692,10 @@
         <v>207</v>
       </c>
       <c r="B232" t="s">
-        <v>209</v>
+        <v>208</v>
+      </c>
+      <c r="C232" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
@@ -5651,10 +5703,7 @@
         <v>207</v>
       </c>
       <c r="B233" t="s">
-        <v>28</v>
-      </c>
-      <c r="C233" t="s">
-        <v>708</v>
+        <v>209</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
@@ -5662,7 +5711,7 @@
         <v>207</v>
       </c>
       <c r="B234" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="C234" t="s">
         <v>708</v>
@@ -5673,10 +5722,10 @@
         <v>207</v>
       </c>
       <c r="B235" t="s">
-        <v>210</v>
-      </c>
-      <c r="E235" t="s">
-        <v>780</v>
+        <v>138</v>
+      </c>
+      <c r="C235" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
@@ -5684,7 +5733,10 @@
         <v>207</v>
       </c>
       <c r="B236" t="s">
-        <v>211</v>
+        <v>210</v>
+      </c>
+      <c r="E236" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
@@ -5692,7 +5744,7 @@
         <v>207</v>
       </c>
       <c r="B237" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
@@ -5700,7 +5752,7 @@
         <v>207</v>
       </c>
       <c r="B238" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
@@ -5708,10 +5760,7 @@
         <v>207</v>
       </c>
       <c r="B239" t="s">
-        <v>214</v>
-      </c>
-      <c r="C239" t="s">
-        <v>742</v>
+        <v>213</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
@@ -5719,10 +5768,10 @@
         <v>207</v>
       </c>
       <c r="B240" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C240" t="s">
-        <v>708</v>
+        <v>742</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
@@ -5730,7 +5779,7 @@
         <v>207</v>
       </c>
       <c r="B241" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C241" t="s">
         <v>708</v>
@@ -5741,7 +5790,7 @@
         <v>207</v>
       </c>
       <c r="B242" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C242" t="s">
         <v>708</v>
@@ -5752,7 +5801,7 @@
         <v>207</v>
       </c>
       <c r="B243" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C243" t="s">
         <v>708</v>
@@ -5763,10 +5812,10 @@
         <v>207</v>
       </c>
       <c r="B244" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C244" t="s">
-        <v>743</v>
+        <v>708</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
@@ -5774,10 +5823,10 @@
         <v>207</v>
       </c>
       <c r="B245" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C245" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
@@ -5785,7 +5834,7 @@
         <v>207</v>
       </c>
       <c r="B246" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C246" t="s">
         <v>708</v>
@@ -5796,7 +5845,7 @@
         <v>207</v>
       </c>
       <c r="B247" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C247" t="s">
         <v>708</v>
@@ -5807,7 +5856,7 @@
         <v>207</v>
       </c>
       <c r="B248" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C248" t="s">
         <v>708</v>
@@ -5818,7 +5867,10 @@
         <v>207</v>
       </c>
       <c r="B249" t="s">
-        <v>224</v>
+        <v>223</v>
+      </c>
+      <c r="C249" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
@@ -5826,10 +5878,7 @@
         <v>207</v>
       </c>
       <c r="B250" t="s">
-        <v>225</v>
-      </c>
-      <c r="D250" t="s">
-        <v>714</v>
+        <v>224</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
@@ -5837,7 +5886,7 @@
         <v>207</v>
       </c>
       <c r="B251" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D251" t="s">
         <v>714</v>
@@ -5848,10 +5897,10 @@
         <v>207</v>
       </c>
       <c r="B252" t="s">
-        <v>227</v>
-      </c>
-      <c r="C252" t="s">
-        <v>708</v>
+        <v>226</v>
+      </c>
+      <c r="D252" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
@@ -5859,7 +5908,7 @@
         <v>207</v>
       </c>
       <c r="B253" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C253" t="s">
         <v>708</v>
@@ -5870,10 +5919,10 @@
         <v>207</v>
       </c>
       <c r="B254" t="s">
-        <v>229</v>
-      </c>
-      <c r="E254" t="s">
-        <v>778</v>
+        <v>228</v>
+      </c>
+      <c r="C254" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
@@ -5881,7 +5930,7 @@
         <v>207</v>
       </c>
       <c r="B255" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E255" t="s">
         <v>778</v>
@@ -5892,7 +5941,7 @@
         <v>207</v>
       </c>
       <c r="B256" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E256" t="s">
         <v>778</v>
@@ -5903,10 +5952,10 @@
         <v>207</v>
       </c>
       <c r="B257" t="s">
-        <v>232</v>
-      </c>
-      <c r="C257" t="s">
-        <v>744</v>
+        <v>231</v>
+      </c>
+      <c r="E257" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
@@ -5914,10 +5963,10 @@
         <v>207</v>
       </c>
       <c r="B258" t="s">
-        <v>233</v>
-      </c>
-      <c r="E258" t="s">
-        <v>778</v>
+        <v>232</v>
+      </c>
+      <c r="C258" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
@@ -5925,7 +5974,7 @@
         <v>207</v>
       </c>
       <c r="B259" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E259" t="s">
         <v>778</v>
@@ -5936,7 +5985,7 @@
         <v>207</v>
       </c>
       <c r="B260" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E260" t="s">
         <v>778</v>
@@ -5947,7 +5996,7 @@
         <v>207</v>
       </c>
       <c r="B261" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E261" t="s">
         <v>778</v>
@@ -5958,7 +6007,7 @@
         <v>207</v>
       </c>
       <c r="B262" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E262" t="s">
         <v>778</v>
@@ -5969,7 +6018,7 @@
         <v>207</v>
       </c>
       <c r="B263" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E263" t="s">
         <v>778</v>
@@ -5980,10 +6029,10 @@
         <v>207</v>
       </c>
       <c r="B264" t="s">
-        <v>239</v>
-      </c>
-      <c r="C264" t="s">
-        <v>22</v>
+        <v>238</v>
+      </c>
+      <c r="E264" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
@@ -5991,10 +6040,10 @@
         <v>207</v>
       </c>
       <c r="B265" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C265" t="s">
-        <v>708</v>
+        <v>22</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
@@ -6002,7 +6051,7 @@
         <v>207</v>
       </c>
       <c r="B266" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C266" t="s">
         <v>708</v>
@@ -6013,7 +6062,10 @@
         <v>207</v>
       </c>
       <c r="B267" t="s">
-        <v>97</v>
+        <v>241</v>
+      </c>
+      <c r="C267" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
@@ -6021,10 +6073,7 @@
         <v>207</v>
       </c>
       <c r="B268" t="s">
-        <v>242</v>
-      </c>
-      <c r="C268" t="s">
-        <v>745</v>
+        <v>97</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
@@ -6032,10 +6081,10 @@
         <v>207</v>
       </c>
       <c r="B269" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C269" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
@@ -6043,10 +6092,10 @@
         <v>207</v>
       </c>
       <c r="B270" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C270" t="s">
-        <v>708</v>
+        <v>744</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
@@ -6054,7 +6103,10 @@
         <v>207</v>
       </c>
       <c r="B271" t="s">
-        <v>245</v>
+        <v>244</v>
+      </c>
+      <c r="C271" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
@@ -6062,7 +6114,7 @@
         <v>207</v>
       </c>
       <c r="B272" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
@@ -6070,7 +6122,7 @@
         <v>207</v>
       </c>
       <c r="B273" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
@@ -6078,7 +6130,7 @@
         <v>207</v>
       </c>
       <c r="B274" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -6086,18 +6138,18 @@
         <v>207</v>
       </c>
       <c r="B275" t="s">
-        <v>249</v>
-      </c>
-      <c r="C275" t="s">
-        <v>790</v>
+        <v>248</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="B276" t="s">
-        <v>251</v>
+        <v>249</v>
+      </c>
+      <c r="C276" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
@@ -6105,7 +6157,7 @@
         <v>250</v>
       </c>
       <c r="B277" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
@@ -6113,7 +6165,7 @@
         <v>250</v>
       </c>
       <c r="B278" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
@@ -6121,7 +6173,7 @@
         <v>250</v>
       </c>
       <c r="B279" t="s">
-        <v>253</v>
+        <v>138</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
@@ -6129,18 +6181,15 @@
         <v>250</v>
       </c>
       <c r="B280" t="s">
-        <v>126</v>
+        <v>253</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B281" t="s">
-        <v>255</v>
-      </c>
-      <c r="C281" t="s">
-        <v>746</v>
+        <v>126</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
@@ -6148,21 +6197,21 @@
         <v>254</v>
       </c>
       <c r="B282" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C282" t="s">
-        <v>256</v>
+        <v>746</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B283" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C283" t="s">
-        <v>708</v>
+        <v>256</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
@@ -6170,7 +6219,7 @@
         <v>257</v>
       </c>
       <c r="B284" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C284" t="s">
         <v>708</v>
@@ -6181,10 +6230,10 @@
         <v>257</v>
       </c>
       <c r="B285" t="s">
-        <v>6</v>
+        <v>259</v>
       </c>
       <c r="C285" t="s">
-        <v>747</v>
+        <v>708</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -6192,10 +6241,10 @@
         <v>257</v>
       </c>
       <c r="B286" t="s">
-        <v>260</v>
+        <v>6</v>
       </c>
       <c r="C286" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
@@ -6203,10 +6252,10 @@
         <v>257</v>
       </c>
       <c r="B287" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C287" t="s">
-        <v>708</v>
+        <v>748</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
@@ -6214,10 +6263,10 @@
         <v>257</v>
       </c>
       <c r="B288" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C288" t="s">
-        <v>252</v>
+        <v>708</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
@@ -6225,7 +6274,10 @@
         <v>257</v>
       </c>
       <c r="B289" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="C289" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
@@ -6233,10 +6285,7 @@
         <v>257</v>
       </c>
       <c r="B290" t="s">
-        <v>264</v>
-      </c>
-      <c r="C290" t="s">
-        <v>127</v>
+        <v>263</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
@@ -6244,10 +6293,10 @@
         <v>257</v>
       </c>
       <c r="B291" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C291" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
@@ -6255,10 +6304,10 @@
         <v>257</v>
       </c>
       <c r="B292" t="s">
-        <v>23</v>
+        <v>265</v>
       </c>
       <c r="C292" t="s">
-        <v>708</v>
+        <v>126</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
@@ -6266,18 +6315,18 @@
         <v>257</v>
       </c>
       <c r="B293" t="s">
-        <v>266</v>
+        <v>23</v>
+      </c>
+      <c r="C293" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B294" t="s">
-        <v>268</v>
-      </c>
-      <c r="C294" t="s">
-        <v>749</v>
+        <v>266</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
@@ -6285,10 +6334,10 @@
         <v>267</v>
       </c>
       <c r="B295" t="s">
-        <v>27</v>
+        <v>268</v>
       </c>
       <c r="C295" t="s">
-        <v>209</v>
+        <v>749</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
@@ -6296,7 +6345,10 @@
         <v>267</v>
       </c>
       <c r="B296" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="C296" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -6304,10 +6356,7 @@
         <v>267</v>
       </c>
       <c r="B297" t="s">
-        <v>269</v>
-      </c>
-      <c r="C297" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -6315,7 +6364,10 @@
         <v>267</v>
       </c>
       <c r="B298" t="s">
-        <v>270</v>
+        <v>269</v>
+      </c>
+      <c r="C298" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
@@ -6323,10 +6375,7 @@
         <v>267</v>
       </c>
       <c r="B299" t="s">
-        <v>271</v>
-      </c>
-      <c r="C299" t="s">
-        <v>756</v>
+        <v>270</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
@@ -6334,7 +6383,10 @@
         <v>267</v>
       </c>
       <c r="B300" t="s">
-        <v>200</v>
+        <v>271</v>
+      </c>
+      <c r="C300" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
@@ -6342,7 +6394,7 @@
         <v>267</v>
       </c>
       <c r="B301" t="s">
-        <v>272</v>
+        <v>200</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
@@ -6350,10 +6402,7 @@
         <v>267</v>
       </c>
       <c r="B302" t="s">
-        <v>273</v>
-      </c>
-      <c r="C302" t="s">
-        <v>740</v>
+        <v>272</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
@@ -6361,7 +6410,10 @@
         <v>267</v>
       </c>
       <c r="B303" t="s">
-        <v>187</v>
+        <v>273</v>
+      </c>
+      <c r="C303" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
@@ -6369,10 +6421,7 @@
         <v>267</v>
       </c>
       <c r="B304" t="s">
-        <v>239</v>
-      </c>
-      <c r="C304" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
@@ -6380,7 +6429,10 @@
         <v>267</v>
       </c>
       <c r="B305" t="s">
-        <v>97</v>
+        <v>239</v>
+      </c>
+      <c r="C305" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
@@ -6388,10 +6440,7 @@
         <v>267</v>
       </c>
       <c r="B306" t="s">
-        <v>203</v>
-      </c>
-      <c r="C306" t="s">
-        <v>705</v>
+        <v>97</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
@@ -6399,7 +6448,10 @@
         <v>267</v>
       </c>
       <c r="B307" t="s">
-        <v>26</v>
+        <v>203</v>
+      </c>
+      <c r="C307" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
@@ -6407,10 +6459,7 @@
         <v>267</v>
       </c>
       <c r="B308" t="s">
-        <v>185</v>
-      </c>
-      <c r="C308" t="s">
-        <v>713</v>
+        <v>26</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
@@ -6418,10 +6467,10 @@
         <v>267</v>
       </c>
       <c r="B309" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C309" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
@@ -6429,7 +6478,7 @@
         <v>267</v>
       </c>
       <c r="B310" t="s">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="C310" t="s">
         <v>708</v>
@@ -6440,7 +6489,7 @@
         <v>267</v>
       </c>
       <c r="B311" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C311" t="s">
         <v>708</v>
@@ -6451,7 +6500,7 @@
         <v>267</v>
       </c>
       <c r="B312" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C312" t="s">
         <v>708</v>
@@ -6462,13 +6511,10 @@
         <v>267</v>
       </c>
       <c r="B313" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C313" t="s">
-        <v>750</v>
-      </c>
-      <c r="D313" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
@@ -6476,7 +6522,13 @@
         <v>267</v>
       </c>
       <c r="B314" t="s">
-        <v>278</v>
+        <v>277</v>
+      </c>
+      <c r="C314" t="s">
+        <v>750</v>
+      </c>
+      <c r="D314" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
@@ -6484,13 +6536,7 @@
         <v>267</v>
       </c>
       <c r="B315" t="s">
-        <v>279</v>
-      </c>
-      <c r="C315" t="s">
-        <v>751</v>
-      </c>
-      <c r="D315" t="s">
-        <v>714</v>
+        <v>278</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
@@ -6498,7 +6544,13 @@
         <v>267</v>
       </c>
       <c r="B316" t="s">
-        <v>280</v>
+        <v>279</v>
+      </c>
+      <c r="C316" t="s">
+        <v>751</v>
+      </c>
+      <c r="D316" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
@@ -6506,13 +6558,7 @@
         <v>267</v>
       </c>
       <c r="B317" t="s">
-        <v>281</v>
-      </c>
-      <c r="C317" t="s">
-        <v>752</v>
-      </c>
-      <c r="D317" t="s">
-        <v>714</v>
+        <v>280</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
@@ -6520,7 +6566,13 @@
         <v>267</v>
       </c>
       <c r="B318" t="s">
-        <v>282</v>
+        <v>281</v>
+      </c>
+      <c r="C318" t="s">
+        <v>752</v>
+      </c>
+      <c r="D318" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
@@ -6528,10 +6580,7 @@
         <v>267</v>
       </c>
       <c r="B319" t="s">
-        <v>283</v>
-      </c>
-      <c r="C319" t="s">
-        <v>708</v>
+        <v>282</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
@@ -6539,7 +6588,7 @@
         <v>267</v>
       </c>
       <c r="B320" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C320" t="s">
         <v>708</v>
@@ -6550,7 +6599,7 @@
         <v>267</v>
       </c>
       <c r="B321" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C321" t="s">
         <v>708</v>
@@ -6558,13 +6607,13 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="B322" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C322" t="s">
-        <v>757</v>
+        <v>708</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
@@ -6572,10 +6621,10 @@
         <v>286</v>
       </c>
       <c r="B323" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="C323" t="s">
-        <v>22</v>
+        <v>757</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
@@ -6583,18 +6632,18 @@
         <v>286</v>
       </c>
       <c r="B324" t="s">
-        <v>288</v>
+        <v>239</v>
+      </c>
+      <c r="C324" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B325" t="s">
-        <v>290</v>
-      </c>
-      <c r="C325" t="s">
-        <v>753</v>
+        <v>288</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
@@ -6602,7 +6651,10 @@
         <v>289</v>
       </c>
       <c r="B326" t="s">
-        <v>97</v>
+        <v>290</v>
+      </c>
+      <c r="C326" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
@@ -6610,10 +6662,7 @@
         <v>289</v>
       </c>
       <c r="B327" t="s">
-        <v>291</v>
-      </c>
-      <c r="C327" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
@@ -6621,7 +6670,10 @@
         <v>289</v>
       </c>
       <c r="B328" t="s">
-        <v>292</v>
+        <v>291</v>
+      </c>
+      <c r="C328" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
@@ -6629,10 +6681,7 @@
         <v>289</v>
       </c>
       <c r="B329" t="s">
-        <v>293</v>
-      </c>
-      <c r="C329" t="s">
-        <v>754</v>
+        <v>292</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -6640,7 +6689,10 @@
         <v>289</v>
       </c>
       <c r="B330" t="s">
-        <v>294</v>
+        <v>293</v>
+      </c>
+      <c r="C330" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
@@ -6648,7 +6700,7 @@
         <v>289</v>
       </c>
       <c r="B331" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
@@ -6656,10 +6708,7 @@
         <v>289</v>
       </c>
       <c r="B332" t="s">
-        <v>296</v>
-      </c>
-      <c r="C332" t="s">
-        <v>708</v>
+        <v>295</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
@@ -6667,7 +6716,7 @@
         <v>289</v>
       </c>
       <c r="B333" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C333" t="s">
         <v>708</v>
@@ -6678,7 +6727,7 @@
         <v>289</v>
       </c>
       <c r="B334" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C334" t="s">
         <v>708</v>
@@ -6689,7 +6738,7 @@
         <v>289</v>
       </c>
       <c r="B335" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C335" t="s">
         <v>708</v>
@@ -6700,7 +6749,10 @@
         <v>289</v>
       </c>
       <c r="B336" t="s">
-        <v>300</v>
+        <v>299</v>
+      </c>
+      <c r="C336" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
@@ -6708,10 +6760,7 @@
         <v>289</v>
       </c>
       <c r="B337" t="s">
-        <v>301</v>
-      </c>
-      <c r="C337" t="s">
-        <v>708</v>
+        <v>300</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
@@ -6719,7 +6768,7 @@
         <v>289</v>
       </c>
       <c r="B338" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C338" t="s">
         <v>708</v>
@@ -6730,7 +6779,7 @@
         <v>289</v>
       </c>
       <c r="B339" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C339" t="s">
         <v>708</v>
@@ -6741,7 +6790,7 @@
         <v>289</v>
       </c>
       <c r="B340" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C340" t="s">
         <v>708</v>
@@ -6752,7 +6801,10 @@
         <v>289</v>
       </c>
       <c r="B341" t="s">
-        <v>305</v>
+        <v>304</v>
+      </c>
+      <c r="C341" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
@@ -6760,10 +6812,7 @@
         <v>289</v>
       </c>
       <c r="B342" t="s">
-        <v>306</v>
-      </c>
-      <c r="C342" t="s">
-        <v>708</v>
+        <v>305</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
@@ -6771,7 +6820,7 @@
         <v>289</v>
       </c>
       <c r="B343" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C343" t="s">
         <v>708</v>
@@ -6782,7 +6831,7 @@
         <v>289</v>
       </c>
       <c r="B344" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C344" t="s">
         <v>708</v>
@@ -6793,7 +6842,7 @@
         <v>289</v>
       </c>
       <c r="B345" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C345" t="s">
         <v>708</v>
@@ -6801,13 +6850,13 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="B346" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C346" t="s">
-        <v>318</v>
+        <v>708</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
@@ -6815,15 +6864,18 @@
         <v>310</v>
       </c>
       <c r="B347" t="s">
-        <v>312</v>
+        <v>311</v>
+      </c>
+      <c r="C347" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B348" t="s">
-        <v>5</v>
+        <v>312</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
@@ -6831,10 +6883,7 @@
         <v>313</v>
       </c>
       <c r="B349" t="s">
-        <v>6</v>
-      </c>
-      <c r="C349" t="s">
-        <v>747</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
@@ -6842,10 +6891,10 @@
         <v>313</v>
       </c>
       <c r="B350" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C350" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
@@ -6853,10 +6902,10 @@
         <v>313</v>
       </c>
       <c r="B351" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C351" t="s">
-        <v>708</v>
+        <v>748</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -6864,7 +6913,7 @@
         <v>313</v>
       </c>
       <c r="B352" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C352" t="s">
         <v>708</v>
@@ -6875,10 +6924,10 @@
         <v>313</v>
       </c>
       <c r="B353" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C353" t="s">
-        <v>127</v>
+        <v>708</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
@@ -6886,10 +6935,10 @@
         <v>313</v>
       </c>
       <c r="B354" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C354" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.2">
@@ -6897,7 +6946,10 @@
         <v>313</v>
       </c>
       <c r="B355" t="s">
-        <v>316</v>
+        <v>315</v>
+      </c>
+      <c r="C355" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.2">
@@ -6905,7 +6957,7 @@
         <v>313</v>
       </c>
       <c r="B356" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
@@ -6913,7 +6965,7 @@
         <v>313</v>
       </c>
       <c r="B357" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
@@ -6921,18 +6973,15 @@
         <v>313</v>
       </c>
       <c r="B358" t="s">
-        <v>23</v>
+        <v>318</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B359" t="s">
-        <v>320</v>
-      </c>
-      <c r="C359" t="s">
-        <v>755</v>
+        <v>23</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.2">
@@ -6940,10 +6989,10 @@
         <v>319</v>
       </c>
       <c r="B360" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
       <c r="C360" t="s">
-        <v>22</v>
+        <v>755</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.2">
@@ -6951,10 +7000,10 @@
         <v>319</v>
       </c>
       <c r="B361" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="C361" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
@@ -6962,7 +7011,10 @@
         <v>319</v>
       </c>
       <c r="B362" t="s">
-        <v>322</v>
+        <v>321</v>
+      </c>
+      <c r="C362" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -6970,7 +7022,7 @@
         <v>319</v>
       </c>
       <c r="B363" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
@@ -6978,10 +7030,7 @@
         <v>319</v>
       </c>
       <c r="B364" t="s">
-        <v>296</v>
-      </c>
-      <c r="C364" t="s">
-        <v>708</v>
+        <v>295</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
@@ -6989,7 +7038,7 @@
         <v>319</v>
       </c>
       <c r="B365" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C365" t="s">
         <v>708</v>
@@ -7000,7 +7049,7 @@
         <v>319</v>
       </c>
       <c r="B366" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C366" t="s">
         <v>708</v>
@@ -7011,7 +7060,7 @@
         <v>319</v>
       </c>
       <c r="B367" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C367" t="s">
         <v>708</v>
@@ -7022,7 +7071,10 @@
         <v>319</v>
       </c>
       <c r="B368" t="s">
-        <v>323</v>
+        <v>299</v>
+      </c>
+      <c r="C368" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
@@ -7030,7 +7082,7 @@
         <v>319</v>
       </c>
       <c r="B369" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
@@ -7038,7 +7090,7 @@
         <v>319</v>
       </c>
       <c r="B370" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.2">
@@ -7046,7 +7098,7 @@
         <v>319</v>
       </c>
       <c r="B371" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.2">
@@ -7054,7 +7106,7 @@
         <v>319</v>
       </c>
       <c r="B372" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
@@ -7062,18 +7114,15 @@
         <v>319</v>
       </c>
       <c r="B373" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B374" t="s">
-        <v>293</v>
-      </c>
-      <c r="C374" t="s">
-        <v>754</v>
+        <v>328</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
@@ -7081,7 +7130,10 @@
         <v>329</v>
       </c>
       <c r="B375" t="s">
-        <v>294</v>
+        <v>293</v>
+      </c>
+      <c r="C375" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
@@ -7089,10 +7141,7 @@
         <v>329</v>
       </c>
       <c r="B376" t="s">
-        <v>239</v>
-      </c>
-      <c r="C376" t="s">
-        <v>22</v>
+        <v>294</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
@@ -7100,7 +7149,10 @@
         <v>329</v>
       </c>
       <c r="B377" t="s">
-        <v>97</v>
+        <v>239</v>
+      </c>
+      <c r="C377" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
@@ -7108,18 +7160,15 @@
         <v>329</v>
       </c>
       <c r="B378" t="s">
-        <v>330</v>
+        <v>97</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B379" t="s">
-        <v>47</v>
-      </c>
-      <c r="C379" t="s">
-        <v>22</v>
+        <v>330</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
@@ -7127,10 +7176,10 @@
         <v>331</v>
       </c>
       <c r="B380" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C380" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
@@ -7138,10 +7187,10 @@
         <v>331</v>
       </c>
       <c r="B381" t="s">
-        <v>332</v>
+        <v>48</v>
       </c>
       <c r="C381" t="s">
-        <v>758</v>
+        <v>97</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
@@ -7149,10 +7198,10 @@
         <v>331</v>
       </c>
       <c r="B382" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C382" t="s">
-        <v>126</v>
+        <v>758</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
@@ -7160,179 +7209,176 @@
         <v>331</v>
       </c>
       <c r="B383" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C383" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B384" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C384" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>335</v>
       </c>
       <c r="B385" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+      <c r="C385" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>335</v>
       </c>
       <c r="B386" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>335</v>
       </c>
       <c r="B387" t="s">
-        <v>338</v>
-      </c>
-      <c r="C387" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>335</v>
       </c>
       <c r="B388" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C388" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>335</v>
       </c>
       <c r="B389" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+      <c r="C389" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>335</v>
       </c>
       <c r="B390" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>335</v>
       </c>
       <c r="B391" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>335</v>
       </c>
       <c r="B392" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>335</v>
       </c>
       <c r="B393" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>335</v>
       </c>
       <c r="B394" t="s">
-        <v>30</v>
-      </c>
-      <c r="C394" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>335</v>
       </c>
       <c r="B395" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C395" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>335</v>
       </c>
       <c r="B396" t="s">
-        <v>295</v>
+        <v>31</v>
       </c>
       <c r="C396" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>335</v>
       </c>
       <c r="B397" t="s">
-        <v>345</v>
+        <v>295</v>
       </c>
       <c r="C397" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>335</v>
       </c>
       <c r="B398" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C398" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>335</v>
       </c>
       <c r="B399" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C399" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>335</v>
       </c>
       <c r="B400" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C400" t="s">
-        <v>759</v>
-      </c>
-      <c r="D400" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.2">
@@ -7340,10 +7386,13 @@
         <v>335</v>
       </c>
       <c r="B401" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C401" t="s">
-        <v>708</v>
+        <v>759</v>
+      </c>
+      <c r="D401" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.2">
@@ -7351,12 +7400,9 @@
         <v>335</v>
       </c>
       <c r="B402" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C402" t="s">
-        <v>760</v>
-      </c>
-      <c r="D402" t="s">
         <v>708</v>
       </c>
     </row>
@@ -7365,10 +7411,10 @@
         <v>335</v>
       </c>
       <c r="B403" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C403" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D403" t="s">
         <v>708</v>
@@ -7379,7 +7425,10 @@
         <v>335</v>
       </c>
       <c r="B404" t="s">
-        <v>352</v>
+        <v>351</v>
+      </c>
+      <c r="C404" t="s">
+        <v>761</v>
       </c>
       <c r="D404" t="s">
         <v>708</v>
@@ -7390,7 +7439,10 @@
         <v>335</v>
       </c>
       <c r="B405" t="s">
-        <v>353</v>
+        <v>352</v>
+      </c>
+      <c r="D405" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.2">
@@ -7398,10 +7450,7 @@
         <v>335</v>
       </c>
       <c r="B406" t="s">
-        <v>354</v>
-      </c>
-      <c r="D406" t="s">
-        <v>714</v>
+        <v>353</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.2">
@@ -7409,10 +7458,10 @@
         <v>335</v>
       </c>
       <c r="B407" t="s">
-        <v>355</v>
-      </c>
-      <c r="C407" t="s">
-        <v>708</v>
+        <v>354</v>
+      </c>
+      <c r="D407" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.2">
@@ -7420,10 +7469,10 @@
         <v>335</v>
       </c>
       <c r="B408" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C408" t="s">
-        <v>762</v>
+        <v>708</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.2">
@@ -7431,10 +7480,10 @@
         <v>335</v>
       </c>
       <c r="B409" t="s">
-        <v>47</v>
-      </c>
-      <c r="D409" t="s">
-        <v>714</v>
+        <v>356</v>
+      </c>
+      <c r="C409" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.2">
@@ -7442,10 +7491,10 @@
         <v>335</v>
       </c>
       <c r="B410" t="s">
-        <v>48</v>
-      </c>
-      <c r="C410" t="s">
-        <v>97</v>
+        <v>47</v>
+      </c>
+      <c r="D410" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.2">
@@ -7453,10 +7502,10 @@
         <v>335</v>
       </c>
       <c r="B411" t="s">
-        <v>357</v>
+        <v>48</v>
       </c>
       <c r="C411" t="s">
-        <v>763</v>
+        <v>97</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.2">
@@ -7464,10 +7513,10 @@
         <v>335</v>
       </c>
       <c r="B412" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C412" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.2">
@@ -7475,10 +7524,10 @@
         <v>335</v>
       </c>
       <c r="B413" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C413" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.2">
@@ -7486,10 +7535,10 @@
         <v>335</v>
       </c>
       <c r="B414" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="C414" t="s">
-        <v>126</v>
+        <v>765</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.2">
@@ -7497,10 +7546,10 @@
         <v>335</v>
       </c>
       <c r="B415" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C415" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.2">
@@ -7508,10 +7557,10 @@
         <v>335</v>
       </c>
       <c r="B416" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="C416" t="s">
-        <v>708</v>
+        <v>127</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.2">
@@ -7519,7 +7568,7 @@
         <v>335</v>
       </c>
       <c r="B417" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C417" t="s">
         <v>708</v>
@@ -7530,7 +7579,7 @@
         <v>335</v>
       </c>
       <c r="B418" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C418" t="s">
         <v>708</v>
@@ -7541,7 +7590,7 @@
         <v>335</v>
       </c>
       <c r="B419" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C419" t="s">
         <v>708</v>
@@ -7552,7 +7601,7 @@
         <v>335</v>
       </c>
       <c r="B420" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C420" t="s">
         <v>708</v>
@@ -7563,7 +7612,7 @@
         <v>335</v>
       </c>
       <c r="B421" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C421" t="s">
         <v>708</v>
@@ -7574,10 +7623,10 @@
         <v>335</v>
       </c>
       <c r="B422" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C422" t="s">
-        <v>766</v>
+        <v>708</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.2">
@@ -7585,10 +7634,10 @@
         <v>335</v>
       </c>
       <c r="B423" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C423" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.2">
@@ -7596,10 +7645,10 @@
         <v>335</v>
       </c>
       <c r="B424" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C424" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.2">
@@ -7607,7 +7656,10 @@
         <v>335</v>
       </c>
       <c r="B425" t="s">
-        <v>138</v>
+        <v>368</v>
+      </c>
+      <c r="C425" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.2">
@@ -7615,7 +7667,7 @@
         <v>335</v>
       </c>
       <c r="B426" t="s">
-        <v>369</v>
+        <v>138</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.2">
@@ -7623,10 +7675,7 @@
         <v>335</v>
       </c>
       <c r="B427" t="s">
-        <v>370</v>
-      </c>
-      <c r="C427" t="s">
-        <v>708</v>
+        <v>369</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.2">
@@ -7634,10 +7683,10 @@
         <v>335</v>
       </c>
       <c r="B428" t="s">
-        <v>371</v>
-      </c>
-      <c r="D428" t="s">
-        <v>769</v>
+        <v>370</v>
+      </c>
+      <c r="C428" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.2">
@@ -7645,7 +7694,7 @@
         <v>335</v>
       </c>
       <c r="B429" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D429" t="s">
         <v>769</v>
@@ -7656,7 +7705,7 @@
         <v>335</v>
       </c>
       <c r="B430" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D430" t="s">
         <v>769</v>
@@ -7667,7 +7716,7 @@
         <v>335</v>
       </c>
       <c r="B431" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D431" t="s">
         <v>769</v>
@@ -7678,7 +7727,7 @@
         <v>335</v>
       </c>
       <c r="B432" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D432" t="s">
         <v>769</v>
@@ -7689,7 +7738,7 @@
         <v>335</v>
       </c>
       <c r="B433" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D433" t="s">
         <v>769</v>
@@ -7700,7 +7749,7 @@
         <v>335</v>
       </c>
       <c r="B434" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D434" t="s">
         <v>769</v>
@@ -7711,7 +7760,7 @@
         <v>335</v>
       </c>
       <c r="B435" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D435" t="s">
         <v>769</v>
@@ -7722,7 +7771,7 @@
         <v>335</v>
       </c>
       <c r="B436" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D436" t="s">
         <v>769</v>
@@ -7733,7 +7782,7 @@
         <v>335</v>
       </c>
       <c r="B437" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D437" t="s">
         <v>769</v>
@@ -7744,7 +7793,7 @@
         <v>335</v>
       </c>
       <c r="B438" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D438" t="s">
         <v>769</v>
@@ -7755,7 +7804,7 @@
         <v>335</v>
       </c>
       <c r="B439" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D439" t="s">
         <v>769</v>
@@ -7766,7 +7815,7 @@
         <v>335</v>
       </c>
       <c r="B440" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D440" t="s">
         <v>769</v>
@@ -7777,7 +7826,7 @@
         <v>335</v>
       </c>
       <c r="B441" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D441" t="s">
         <v>769</v>
@@ -7788,7 +7837,7 @@
         <v>335</v>
       </c>
       <c r="B442" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D442" t="s">
         <v>769</v>
@@ -7799,7 +7848,7 @@
         <v>335</v>
       </c>
       <c r="B443" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D443" t="s">
         <v>769</v>
@@ -7810,7 +7859,7 @@
         <v>335</v>
       </c>
       <c r="B444" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D444" t="s">
         <v>769</v>
@@ -7821,7 +7870,7 @@
         <v>335</v>
       </c>
       <c r="B445" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D445" t="s">
         <v>769</v>
@@ -7832,7 +7881,7 @@
         <v>335</v>
       </c>
       <c r="B446" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D446" t="s">
         <v>769</v>
@@ -7843,7 +7892,7 @@
         <v>335</v>
       </c>
       <c r="B447" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D447" t="s">
         <v>769</v>
@@ -7854,7 +7903,7 @@
         <v>335</v>
       </c>
       <c r="B448" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D448" t="s">
         <v>769</v>
@@ -7865,7 +7914,7 @@
         <v>335</v>
       </c>
       <c r="B449" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D449" t="s">
         <v>769</v>
@@ -7876,10 +7925,10 @@
         <v>335</v>
       </c>
       <c r="B450" t="s">
-        <v>393</v>
-      </c>
-      <c r="C450" t="s">
-        <v>714</v>
+        <v>392</v>
+      </c>
+      <c r="D450" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.2">
@@ -7887,10 +7936,10 @@
         <v>335</v>
       </c>
       <c r="B451" t="s">
-        <v>272</v>
+        <v>393</v>
       </c>
       <c r="C451" t="s">
-        <v>770</v>
+        <v>714</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.2">
@@ -7898,10 +7947,10 @@
         <v>335</v>
       </c>
       <c r="B452" t="s">
-        <v>394</v>
+        <v>272</v>
       </c>
       <c r="C452" t="s">
-        <v>708</v>
+        <v>770</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.2">
@@ -7909,7 +7958,7 @@
         <v>335</v>
       </c>
       <c r="B453" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C453" t="s">
         <v>708</v>
@@ -7917,10 +7966,10 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>396</v>
+        <v>335</v>
       </c>
       <c r="B454" t="s">
-        <v>5</v>
+        <v>395</v>
       </c>
       <c r="C454" t="s">
         <v>708</v>
@@ -7931,10 +7980,10 @@
         <v>396</v>
       </c>
       <c r="B455" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C455" t="s">
-        <v>747</v>
+        <v>708</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.2">
@@ -7942,10 +7991,10 @@
         <v>396</v>
       </c>
       <c r="B456" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C456" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.2">
@@ -7953,10 +8002,10 @@
         <v>396</v>
       </c>
       <c r="B457" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C457" t="s">
-        <v>708</v>
+        <v>748</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.2">
@@ -7964,7 +8013,7 @@
         <v>396</v>
       </c>
       <c r="B458" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C458" t="s">
         <v>708</v>
@@ -7975,10 +8024,10 @@
         <v>396</v>
       </c>
       <c r="B459" t="s">
-        <v>314</v>
+        <v>9</v>
       </c>
       <c r="C459" t="s">
-        <v>127</v>
+        <v>708</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.2">
@@ -7986,10 +8035,10 @@
         <v>396</v>
       </c>
       <c r="B460" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C460" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.2">
@@ -7997,7 +8046,10 @@
         <v>396</v>
       </c>
       <c r="B461" t="s">
-        <v>316</v>
+        <v>315</v>
+      </c>
+      <c r="C461" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.2">
@@ -8005,7 +8057,7 @@
         <v>396</v>
       </c>
       <c r="B462" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.2">
@@ -8013,7 +8065,7 @@
         <v>396</v>
       </c>
       <c r="B463" t="s">
-        <v>22</v>
+        <v>317</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.2">
@@ -8021,15 +8073,15 @@
         <v>396</v>
       </c>
       <c r="B464" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B465" t="s">
-        <v>398</v>
+        <v>23</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.2">
@@ -8037,7 +8089,7 @@
         <v>397</v>
       </c>
       <c r="B466" t="s">
-        <v>22</v>
+        <v>398</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.2">
@@ -8045,7 +8097,7 @@
         <v>397</v>
       </c>
       <c r="B467" t="s">
-        <v>399</v>
+        <v>22</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.2">
@@ -8053,7 +8105,7 @@
         <v>397</v>
       </c>
       <c r="B468" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.2">
@@ -8061,7 +8113,7 @@
         <v>397</v>
       </c>
       <c r="B469" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.2">
@@ -8069,7 +8121,7 @@
         <v>397</v>
       </c>
       <c r="B470" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.2">
@@ -8077,13 +8129,7 @@
         <v>397</v>
       </c>
       <c r="B471" t="s">
-        <v>403</v>
-      </c>
-      <c r="C471" t="s">
-        <v>708</v>
-      </c>
-      <c r="E471" t="s">
-        <v>783</v>
+        <v>402</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.2">
@@ -8091,7 +8137,13 @@
         <v>397</v>
       </c>
       <c r="B472" t="s">
-        <v>40</v>
+        <v>403</v>
+      </c>
+      <c r="C472" t="s">
+        <v>708</v>
+      </c>
+      <c r="E472" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.2">
@@ -8099,10 +8151,7 @@
         <v>397</v>
       </c>
       <c r="B473" t="s">
-        <v>404</v>
-      </c>
-      <c r="C473" t="s">
-        <v>771</v>
+        <v>40</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.2">
@@ -8110,7 +8159,10 @@
         <v>397</v>
       </c>
       <c r="B474" t="s">
-        <v>405</v>
+        <v>404</v>
+      </c>
+      <c r="C474" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.2">
@@ -8118,10 +8170,7 @@
         <v>397</v>
       </c>
       <c r="B475" t="s">
-        <v>406</v>
-      </c>
-      <c r="C475" t="s">
-        <v>708</v>
+        <v>405</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.2">
@@ -8129,7 +8178,10 @@
         <v>397</v>
       </c>
       <c r="B476" t="s">
-        <v>407</v>
+        <v>406</v>
+      </c>
+      <c r="C476" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.2">
@@ -8137,10 +8189,7 @@
         <v>397</v>
       </c>
       <c r="B477" t="s">
-        <v>408</v>
-      </c>
-      <c r="C477" t="s">
-        <v>708</v>
+        <v>407</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.2">
@@ -8148,7 +8197,10 @@
         <v>397</v>
       </c>
       <c r="B478" t="s">
-        <v>409</v>
+        <v>408</v>
+      </c>
+      <c r="C478" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.2">
@@ -8156,7 +8208,7 @@
         <v>397</v>
       </c>
       <c r="B479" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.2">
@@ -8164,7 +8216,7 @@
         <v>397</v>
       </c>
       <c r="B480" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.2">
@@ -8172,7 +8224,7 @@
         <v>397</v>
       </c>
       <c r="B481" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.2">
@@ -8180,7 +8232,7 @@
         <v>397</v>
       </c>
       <c r="B482" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.2">
@@ -8188,10 +8240,7 @@
         <v>397</v>
       </c>
       <c r="B483" t="s">
-        <v>103</v>
-      </c>
-      <c r="C483" t="s">
-        <v>708</v>
+        <v>413</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.2">
@@ -8199,7 +8248,7 @@
         <v>397</v>
       </c>
       <c r="B484" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C484" t="s">
         <v>708</v>
@@ -8210,7 +8259,7 @@
         <v>397</v>
       </c>
       <c r="B485" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C485" t="s">
         <v>708</v>
@@ -8221,7 +8270,7 @@
         <v>397</v>
       </c>
       <c r="B486" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C486" t="s">
         <v>708</v>
@@ -8232,21 +8281,21 @@
         <v>397</v>
       </c>
       <c r="B487" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C487" t="s">
-        <v>737</v>
+        <v>708</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B488" t="s">
-        <v>415</v>
+        <v>107</v>
       </c>
       <c r="C488" t="s">
-        <v>772</v>
+        <v>737</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.2">
@@ -8254,7 +8303,10 @@
         <v>414</v>
       </c>
       <c r="B489" t="s">
-        <v>209</v>
+        <v>415</v>
+      </c>
+      <c r="C489" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.2">
@@ -8262,7 +8314,7 @@
         <v>414</v>
       </c>
       <c r="B490" t="s">
-        <v>28</v>
+        <v>209</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.2">
@@ -8270,7 +8322,7 @@
         <v>414</v>
       </c>
       <c r="B491" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.2">
@@ -8278,7 +8330,7 @@
         <v>414</v>
       </c>
       <c r="B492" t="s">
-        <v>416</v>
+        <v>138</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.2">
@@ -8286,7 +8338,7 @@
         <v>414</v>
       </c>
       <c r="B493" t="s">
-        <v>211</v>
+        <v>416</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.2">
@@ -8294,7 +8346,7 @@
         <v>414</v>
       </c>
       <c r="B494" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.2">
@@ -8302,10 +8354,7 @@
         <v>414</v>
       </c>
       <c r="B495" t="s">
-        <v>214</v>
-      </c>
-      <c r="C495" t="s">
-        <v>742</v>
+        <v>213</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.2">
@@ -8313,10 +8362,10 @@
         <v>414</v>
       </c>
       <c r="B496" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C496" t="s">
-        <v>708</v>
+        <v>742</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
@@ -8324,7 +8373,7 @@
         <v>414</v>
       </c>
       <c r="B497" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C497" t="s">
         <v>708</v>
@@ -8335,7 +8384,7 @@
         <v>414</v>
       </c>
       <c r="B498" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C498" t="s">
         <v>708</v>
@@ -8346,7 +8395,7 @@
         <v>414</v>
       </c>
       <c r="B499" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C499" t="s">
         <v>708</v>
@@ -8357,10 +8406,10 @@
         <v>414</v>
       </c>
       <c r="B500" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C500" t="s">
-        <v>743</v>
+        <v>708</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.2">
@@ -8368,10 +8417,10 @@
         <v>414</v>
       </c>
       <c r="B501" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C501" t="s">
-        <v>708</v>
+        <v>743</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.2">
@@ -8379,7 +8428,7 @@
         <v>414</v>
       </c>
       <c r="B502" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C502" t="s">
         <v>708</v>
@@ -8390,7 +8439,7 @@
         <v>414</v>
       </c>
       <c r="B503" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C503" t="s">
         <v>708</v>
@@ -8401,7 +8450,7 @@
         <v>414</v>
       </c>
       <c r="B504" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C504" t="s">
         <v>708</v>
@@ -8412,7 +8461,10 @@
         <v>414</v>
       </c>
       <c r="B505" t="s">
-        <v>224</v>
+        <v>223</v>
+      </c>
+      <c r="C505" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.2">
@@ -8420,7 +8472,7 @@
         <v>414</v>
       </c>
       <c r="B506" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.2">
@@ -8428,10 +8480,7 @@
         <v>414</v>
       </c>
       <c r="B507" t="s">
-        <v>417</v>
-      </c>
-      <c r="C507" t="s">
-        <v>708</v>
+        <v>225</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
@@ -8439,7 +8488,7 @@
         <v>414</v>
       </c>
       <c r="B508" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C508" t="s">
         <v>708</v>
@@ -8450,7 +8499,7 @@
         <v>414</v>
       </c>
       <c r="B509" t="s">
-        <v>226</v>
+        <v>418</v>
       </c>
       <c r="C509" t="s">
         <v>708</v>
@@ -8461,7 +8510,10 @@
         <v>414</v>
       </c>
       <c r="B510" t="s">
-        <v>419</v>
+        <v>226</v>
+      </c>
+      <c r="C510" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.2">
@@ -8469,7 +8521,7 @@
         <v>414</v>
       </c>
       <c r="B511" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.2">
@@ -8477,7 +8529,7 @@
         <v>414</v>
       </c>
       <c r="B512" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.2">
@@ -8485,7 +8537,7 @@
         <v>414</v>
       </c>
       <c r="B513" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.2">
@@ -8493,10 +8545,7 @@
         <v>414</v>
       </c>
       <c r="B514" t="s">
-        <v>423</v>
-      </c>
-      <c r="C514" t="s">
-        <v>708</v>
+        <v>422</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.2">
@@ -8504,7 +8553,10 @@
         <v>414</v>
       </c>
       <c r="B515" t="s">
-        <v>424</v>
+        <v>423</v>
+      </c>
+      <c r="C515" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.2">
@@ -8512,10 +8564,7 @@
         <v>414</v>
       </c>
       <c r="B516" t="s">
-        <v>229</v>
-      </c>
-      <c r="E516" t="s">
-        <v>500</v>
+        <v>424</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.2">
@@ -8523,7 +8572,7 @@
         <v>414</v>
       </c>
       <c r="B517" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E517" t="s">
         <v>500</v>
@@ -8534,7 +8583,7 @@
         <v>414</v>
       </c>
       <c r="B518" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E518" t="s">
         <v>500</v>
@@ -8545,7 +8594,7 @@
         <v>414</v>
       </c>
       <c r="B519" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E519" t="s">
         <v>500</v>
@@ -8556,7 +8605,7 @@
         <v>414</v>
       </c>
       <c r="B520" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E520" t="s">
         <v>500</v>
@@ -8567,7 +8616,7 @@
         <v>414</v>
       </c>
       <c r="B521" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E521" t="s">
         <v>500</v>
@@ -8578,7 +8627,7 @@
         <v>414</v>
       </c>
       <c r="B522" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E522" t="s">
         <v>500</v>
@@ -8589,7 +8638,7 @@
         <v>414</v>
       </c>
       <c r="B523" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E523" t="s">
         <v>500</v>
@@ -8600,7 +8649,7 @@
         <v>414</v>
       </c>
       <c r="B524" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E524" t="s">
         <v>500</v>
@@ -8611,10 +8660,10 @@
         <v>414</v>
       </c>
       <c r="B525" t="s">
-        <v>239</v>
-      </c>
-      <c r="C525" t="s">
-        <v>22</v>
+        <v>238</v>
+      </c>
+      <c r="E525" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.2">
@@ -8622,10 +8671,10 @@
         <v>414</v>
       </c>
       <c r="B526" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C526" t="s">
-        <v>708</v>
+        <v>22</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.2">
@@ -8633,7 +8682,7 @@
         <v>414</v>
       </c>
       <c r="B527" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C527" t="s">
         <v>708</v>
@@ -8644,7 +8693,10 @@
         <v>414</v>
       </c>
       <c r="B528" t="s">
-        <v>97</v>
+        <v>241</v>
+      </c>
+      <c r="C528" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.2">
@@ -8652,10 +8704,7 @@
         <v>414</v>
       </c>
       <c r="B529" t="s">
-        <v>425</v>
-      </c>
-      <c r="C529" t="s">
-        <v>773</v>
+        <v>97</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.2">
@@ -8663,10 +8712,10 @@
         <v>414</v>
       </c>
       <c r="B530" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C530" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.2">
@@ -8674,7 +8723,10 @@
         <v>414</v>
       </c>
       <c r="B531" t="s">
-        <v>248</v>
+        <v>426</v>
+      </c>
+      <c r="C531" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.2">
@@ -8682,7 +8734,7 @@
         <v>414</v>
       </c>
       <c r="B532" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.2">
@@ -8690,18 +8742,18 @@
         <v>414</v>
       </c>
       <c r="B533" t="s">
-        <v>249</v>
-      </c>
-      <c r="C533" t="s">
-        <v>775</v>
+        <v>212</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="B534" t="s">
-        <v>138</v>
+        <v>249</v>
+      </c>
+      <c r="C534" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.2">
@@ -8709,7 +8761,7 @@
         <v>427</v>
       </c>
       <c r="B535" t="s">
-        <v>428</v>
+        <v>138</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.2">
@@ -8717,7 +8769,7 @@
         <v>427</v>
       </c>
       <c r="B536" t="s">
-        <v>100</v>
+        <v>428</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.2">
@@ -8725,7 +8777,7 @@
         <v>427</v>
       </c>
       <c r="B537" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.2">
@@ -8733,7 +8785,7 @@
         <v>427</v>
       </c>
       <c r="B538" t="s">
-        <v>429</v>
+        <v>101</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.2">
@@ -8741,7 +8793,7 @@
         <v>427</v>
       </c>
       <c r="B539" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.2">
@@ -8749,7 +8801,7 @@
         <v>427</v>
       </c>
       <c r="B540" t="s">
-        <v>243</v>
+        <v>430</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.2">
@@ -8757,10 +8809,7 @@
         <v>427</v>
       </c>
       <c r="B541" t="s">
-        <v>412</v>
-      </c>
-      <c r="E541" t="s">
-        <v>782</v>
+        <v>243</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.2">
@@ -8768,10 +8817,10 @@
         <v>427</v>
       </c>
       <c r="B542" t="s">
-        <v>431</v>
-      </c>
-      <c r="C542" t="s">
-        <v>708</v>
+        <v>412</v>
+      </c>
+      <c r="E542" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.2">
@@ -8779,10 +8828,10 @@
         <v>427</v>
       </c>
       <c r="B543" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C543" t="s">
-        <v>305</v>
+        <v>708</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.2">
@@ -8790,10 +8839,10 @@
         <v>427</v>
       </c>
       <c r="B544" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C544" t="s">
-        <v>708</v>
+        <v>305</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.2">
@@ -8801,7 +8850,7 @@
         <v>427</v>
       </c>
       <c r="B545" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C545" t="s">
         <v>708</v>
@@ -8812,7 +8861,7 @@
         <v>427</v>
       </c>
       <c r="B546" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C546" t="s">
         <v>708</v>
@@ -8823,7 +8872,7 @@
         <v>427</v>
       </c>
       <c r="B547" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C547" t="s">
         <v>708</v>
@@ -8834,10 +8883,10 @@
         <v>427</v>
       </c>
       <c r="B548" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C548" t="s">
-        <v>300</v>
+        <v>708</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.2">
@@ -8845,10 +8894,10 @@
         <v>427</v>
       </c>
       <c r="B549" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C549" t="s">
-        <v>708</v>
+        <v>300</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.2">
@@ -8856,7 +8905,7 @@
         <v>427</v>
       </c>
       <c r="B550" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C550" t="s">
         <v>708</v>
@@ -8867,7 +8916,7 @@
         <v>427</v>
       </c>
       <c r="B551" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C551" t="s">
         <v>708</v>
@@ -8878,7 +8927,7 @@
         <v>427</v>
       </c>
       <c r="B552" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C552" t="s">
         <v>708</v>
@@ -8889,10 +8938,10 @@
         <v>427</v>
       </c>
       <c r="B553" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C553" t="s">
-        <v>738</v>
+        <v>708</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.2">
@@ -8900,10 +8949,10 @@
         <v>427</v>
       </c>
       <c r="B554" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C554" t="s">
-        <v>708</v>
+        <v>738</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.2">
@@ -8911,7 +8960,7 @@
         <v>427</v>
       </c>
       <c r="B555" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C555" t="s">
         <v>708</v>
@@ -8922,7 +8971,7 @@
         <v>427</v>
       </c>
       <c r="B556" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C556" t="s">
         <v>708</v>
@@ -8933,7 +8982,7 @@
         <v>427</v>
       </c>
       <c r="B557" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C557" t="s">
         <v>708</v>
@@ -8944,10 +8993,10 @@
         <v>427</v>
       </c>
       <c r="B558" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C558" t="s">
-        <v>737</v>
+        <v>708</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.2">
@@ -8955,10 +9004,10 @@
         <v>427</v>
       </c>
       <c r="B559" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C559" t="s">
-        <v>708</v>
+        <v>737</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.2">
@@ -8966,7 +9015,7 @@
         <v>427</v>
       </c>
       <c r="B560" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C560" t="s">
         <v>708</v>
@@ -8977,7 +9026,7 @@
         <v>427</v>
       </c>
       <c r="B561" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C561" t="s">
         <v>708</v>
@@ -8988,7 +9037,10 @@
         <v>427</v>
       </c>
       <c r="B562" t="s">
-        <v>451</v>
+        <v>450</v>
+      </c>
+      <c r="C562" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.2">
@@ -8996,10 +9048,7 @@
         <v>427</v>
       </c>
       <c r="B563" t="s">
-        <v>452</v>
-      </c>
-      <c r="C563" t="s">
-        <v>22</v>
+        <v>451</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.2">
@@ -9007,7 +9056,10 @@
         <v>427</v>
       </c>
       <c r="B564" t="s">
-        <v>97</v>
+        <v>452</v>
+      </c>
+      <c r="C564" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.2">
@@ -9015,13 +9067,7 @@
         <v>427</v>
       </c>
       <c r="B565" t="s">
-        <v>453</v>
-      </c>
-      <c r="C565" t="s">
-        <v>714</v>
-      </c>
-      <c r="E565" t="s">
-        <v>781</v>
+        <v>97</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.2">
@@ -9029,7 +9075,13 @@
         <v>427</v>
       </c>
       <c r="B566" t="s">
-        <v>34</v>
+        <v>453</v>
+      </c>
+      <c r="C566" t="s">
+        <v>714</v>
+      </c>
+      <c r="E566" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.2">
@@ -9037,7 +9089,7 @@
         <v>427</v>
       </c>
       <c r="B567" t="s">
-        <v>454</v>
+        <v>34</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.2">
@@ -9045,10 +9097,7 @@
         <v>427</v>
       </c>
       <c r="B568" t="s">
-        <v>455</v>
-      </c>
-      <c r="C568" t="s">
-        <v>708</v>
+        <v>454</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.2">
@@ -9056,7 +9105,7 @@
         <v>427</v>
       </c>
       <c r="B569" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C569" t="s">
         <v>708</v>
@@ -9067,7 +9116,10 @@
         <v>427</v>
       </c>
       <c r="B570" t="s">
-        <v>127</v>
+        <v>456</v>
+      </c>
+      <c r="C570" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.2">
@@ -9075,7 +9127,7 @@
         <v>427</v>
       </c>
       <c r="B571" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.2">
@@ -9083,7 +9135,7 @@
         <v>427</v>
       </c>
       <c r="B572" t="s">
-        <v>457</v>
+        <v>126</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.2">
@@ -9091,7 +9143,7 @@
         <v>427</v>
       </c>
       <c r="B573" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.2">
@@ -9099,7 +9151,7 @@
         <v>427</v>
       </c>
       <c r="B574" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.2">
@@ -9107,21 +9159,18 @@
         <v>427</v>
       </c>
       <c r="B575" t="s">
-        <v>460</v>
-      </c>
-      <c r="C575" t="s">
-        <v>708</v>
+        <v>459</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
       <c r="B576" t="s">
-        <v>98</v>
+        <v>460</v>
       </c>
       <c r="C576" t="s">
-        <v>802</v>
+        <v>708</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.2">
@@ -9129,7 +9178,7 @@
         <v>461</v>
       </c>
       <c r="B577" t="s">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="C577" t="s">
         <v>802</v>
@@ -9140,7 +9189,7 @@
         <v>461</v>
       </c>
       <c r="B578" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="C578" t="s">
         <v>802</v>
@@ -9151,7 +9200,7 @@
         <v>461</v>
       </c>
       <c r="B579" t="s">
-        <v>336</v>
+        <v>95</v>
       </c>
       <c r="C579" t="s">
         <v>802</v>
@@ -9162,7 +9211,7 @@
         <v>461</v>
       </c>
       <c r="B580" t="s">
-        <v>462</v>
+        <v>336</v>
       </c>
       <c r="C580" t="s">
         <v>802</v>
@@ -9173,7 +9222,7 @@
         <v>461</v>
       </c>
       <c r="B581" t="s">
-        <v>47</v>
+        <v>462</v>
       </c>
       <c r="C581" t="s">
         <v>802</v>
@@ -9184,7 +9233,7 @@
         <v>461</v>
       </c>
       <c r="B582" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C582" t="s">
         <v>802</v>
@@ -9195,13 +9244,10 @@
         <v>461</v>
       </c>
       <c r="B583" t="s">
-        <v>463</v>
+        <v>48</v>
       </c>
       <c r="C583" t="s">
         <v>802</v>
-      </c>
-      <c r="D583" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.2">
@@ -9209,13 +9255,13 @@
         <v>461</v>
       </c>
       <c r="B584" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C584" t="s">
         <v>802</v>
       </c>
-      <c r="E584" t="s">
-        <v>779</v>
+      <c r="D584" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.2">
@@ -9223,10 +9269,13 @@
         <v>461</v>
       </c>
       <c r="B585" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C585" t="s">
         <v>802</v>
+      </c>
+      <c r="E585" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.2">
@@ -9234,7 +9283,7 @@
         <v>461</v>
       </c>
       <c r="B586" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C586" t="s">
         <v>802</v>
@@ -9245,7 +9294,7 @@
         <v>461</v>
       </c>
       <c r="B587" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C587" t="s">
         <v>802</v>
@@ -9256,7 +9305,7 @@
         <v>461</v>
       </c>
       <c r="B588" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C588" t="s">
         <v>802</v>
@@ -9267,7 +9316,7 @@
         <v>461</v>
       </c>
       <c r="B589" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C589" t="s">
         <v>802</v>
@@ -9278,7 +9327,7 @@
         <v>461</v>
       </c>
       <c r="B590" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C590" t="s">
         <v>802</v>
@@ -9289,7 +9338,7 @@
         <v>461</v>
       </c>
       <c r="B591" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C591" t="s">
         <v>802</v>
@@ -9300,7 +9349,7 @@
         <v>461</v>
       </c>
       <c r="B592" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C592" t="s">
         <v>802</v>
@@ -9311,7 +9360,7 @@
         <v>461</v>
       </c>
       <c r="B593" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C593" t="s">
         <v>802</v>
@@ -9322,7 +9371,7 @@
         <v>461</v>
       </c>
       <c r="B594" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C594" t="s">
         <v>802</v>
@@ -9333,7 +9382,7 @@
         <v>461</v>
       </c>
       <c r="B595" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C595" t="s">
         <v>802</v>
@@ -9344,7 +9393,7 @@
         <v>461</v>
       </c>
       <c r="B596" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C596" t="s">
         <v>802</v>
@@ -9355,7 +9404,7 @@
         <v>461</v>
       </c>
       <c r="B597" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C597" t="s">
         <v>802</v>
@@ -9366,7 +9415,7 @@
         <v>461</v>
       </c>
       <c r="B598" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C598" t="s">
         <v>802</v>
@@ -9377,7 +9426,7 @@
         <v>461</v>
       </c>
       <c r="B599" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C599" t="s">
         <v>802</v>
@@ -9388,7 +9437,7 @@
         <v>461</v>
       </c>
       <c r="B600" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C600" t="s">
         <v>802</v>
@@ -9399,7 +9448,7 @@
         <v>461</v>
       </c>
       <c r="B601" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C601" t="s">
         <v>802</v>
@@ -9410,7 +9459,7 @@
         <v>461</v>
       </c>
       <c r="B602" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C602" t="s">
         <v>802</v>
@@ -9421,7 +9470,7 @@
         <v>461</v>
       </c>
       <c r="B603" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C603" t="s">
         <v>802</v>
@@ -9432,7 +9481,7 @@
         <v>461</v>
       </c>
       <c r="B604" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C604" t="s">
         <v>802</v>
@@ -9443,7 +9492,7 @@
         <v>461</v>
       </c>
       <c r="B605" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C605" t="s">
         <v>802</v>
@@ -9454,7 +9503,7 @@
         <v>461</v>
       </c>
       <c r="B606" t="s">
-        <v>134</v>
+        <v>485</v>
       </c>
       <c r="C606" t="s">
         <v>802</v>
@@ -9465,13 +9514,10 @@
         <v>461</v>
       </c>
       <c r="B607" t="s">
-        <v>486</v>
+        <v>134</v>
       </c>
       <c r="C607" t="s">
-        <v>801</v>
-      </c>
-      <c r="D607" t="s">
-        <v>769</v>
+        <v>802</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.2">
@@ -9479,7 +9525,7 @@
         <v>461</v>
       </c>
       <c r="B608" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C608" t="s">
         <v>801</v>
@@ -9493,7 +9539,7 @@
         <v>461</v>
       </c>
       <c r="B609" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C609" t="s">
         <v>801</v>
@@ -9507,12 +9553,26 @@
         <v>461</v>
       </c>
       <c r="B610" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C610" t="s">
         <v>801</v>
       </c>
       <c r="D610" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A611" t="s">
+        <v>461</v>
+      </c>
+      <c r="B611" t="s">
+        <v>489</v>
+      </c>
+      <c r="C611" t="s">
+        <v>801</v>
+      </c>
+      <c r="D611" t="s">
         <v>769</v>
       </c>
     </row>
